--- a/Result/profitability/3390.xlsx
+++ b/Result/profitability/3390.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.035</v>
+        <v>-0.07500000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>16.0675</v>
+        <v>15.28625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03000000000000001</v>
+        <v>-0.09875</v>
       </c>
       <c r="N3" t="n">
-        <v>16.2775</v>
+        <v>15.16625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.61</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01624999999999999</v>
+        <v>-0.0325</v>
       </c>
       <c r="N4" t="n">
-        <v>16.87375</v>
+        <v>16.14</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03999999999999999</v>
+        <v>0.10625</v>
       </c>
       <c r="N5" t="n">
-        <v>17.3425</v>
+        <v>17.63125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1575</v>
+        <v>0.10875</v>
       </c>
       <c r="N6" t="n">
-        <v>18.465</v>
+        <v>18.115</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24875</v>
+        <v>0.19</v>
       </c>
       <c r="N7" t="n">
-        <v>21.04</v>
+        <v>20.2525</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.37125</v>
+        <v>0.355</v>
       </c>
       <c r="N8" t="n">
-        <v>23.11</v>
+        <v>22.4375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="N12" t="n">
         <v>25.295</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>276</v>
+      </c>
+      <c r="D75" t="n">
+        <v>246</v>
+      </c>
+      <c r="E75" t="n">
+        <v>30</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.9075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7222222222222223</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.380000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6309523809523809</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2733727810650888</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
